--- a/Agriculture/B1_Model_Structure.xlsx
+++ b/Agriculture/B1_Model_Structure.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573C4D9B-E6E8-41E0-9669-53FA17263AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{573C4D9B-E6E8-41E0-9669-53FA17263AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0407743-9A9B-450A-8DAE-9EFDBB93C58E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sets" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Author</author>
+    <author>Autor</author>
   </authors>
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0" xr:uid="{4D80EF67-AF54-4A91-91D6-06FE539D03B9}">
@@ -1446,7 +1446,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1468,6 +1468,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1574,7 +1580,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1616,6 +1622,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{FE58332D-116D-48F4-B441-2561D2F31C64}"/>
@@ -1910,7 +1917,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L291"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -3447,7 +3454,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8A1DB5-AB21-4E2D-94E4-FE18AAF65A94}">
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.21875" customWidth="1"/>
@@ -4009,7 +4016,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A61DBA02-50DA-45DC-88DC-E3B8D7B75762}">
   <dimension ref="A1:AR9"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
@@ -4849,7 +4856,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED10C39E-557A-4278-BB05-98C0EDA618C0}">
   <dimension ref="A1:G118"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.109375" customWidth="1"/>
@@ -4885,26 +4892,26 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="17" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="17" t="s">
         <v>317</v>
       </c>
     </row>
@@ -5173,123 +5180,123 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="17" t="s">
         <v>41</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C27" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="C27" s="17"/>
       <c r="D27" s="3" t="s">
-        <v>317</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="17" t="s">
         <v>42</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C28" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="C28" s="17"/>
       <c r="D28" s="3" t="s">
-        <v>317</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="17" t="s">
         <v>244</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C29" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="C29" s="17"/>
       <c r="D29" s="3" t="s">
-        <v>317</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="17" t="s">
         <v>245</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C30" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="C30" s="17"/>
       <c r="D30" s="3" t="s">
-        <v>317</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="17" t="s">
         <v>246</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C31" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="C31" s="17"/>
       <c r="D31" s="3" t="s">
-        <v>317</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="17" t="s">
         <v>247</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C32" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="C32" s="17"/>
       <c r="D32" s="3" t="s">
-        <v>317</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="17" t="s">
         <v>248</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C33" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="C33" s="17"/>
       <c r="D33" s="3" t="s">
-        <v>317</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="17" t="s">
         <v>249</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C34" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="C34" s="17"/>
       <c r="D34" s="3" t="s">
-        <v>317</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="17" t="s">
         <v>250</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C35" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="C35" s="17"/>
       <c r="D35" s="3" t="s">
-        <v>317</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="17" t="s">
         <v>251</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C36" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="C36" s="17"/>
       <c r="D36" s="3" t="s">
-        <v>317</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -6134,98 +6141,98 @@
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="3" t="s">
+      <c r="A107" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3" t="s">
+      <c r="C107" s="17"/>
+      <c r="D107" s="17" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3" t="s">
+      <c r="C108" s="17"/>
+      <c r="D108" s="17" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="3" t="s">
+      <c r="A109" s="17" t="s">
         <v>309</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3" t="s">
+      <c r="C109" s="17"/>
+      <c r="D109" s="17" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" s="3" t="s">
+      <c r="A110" s="17" t="s">
         <v>310</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3" t="s">
+      <c r="C110" s="17"/>
+      <c r="D110" s="17" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="3" t="s">
+      <c r="A111" s="17" t="s">
         <v>311</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3" t="s">
+      <c r="C111" s="17"/>
+      <c r="D111" s="17" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="3" t="s">
+      <c r="A112" s="17" t="s">
         <v>312</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3" t="s">
+      <c r="C112" s="17"/>
+      <c r="D112" s="17" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="3" t="s">
+      <c r="A113" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3" t="s">
+      <c r="C113" s="17"/>
+      <c r="D113" s="17" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="3" t="s">
+      <c r="A114" s="17" t="s">
         <v>314</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3" t="s">
+      <c r="C114" s="17"/>
+      <c r="D114" s="17" t="s">
         <v>317</v>
       </c>
     </row>
@@ -6299,8 +6306,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B8F814574E960A4499025803604D4DF4" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="314e7041d7d1561dbe33e80becf1c782">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b2ff61d-e0c4-454b-ba72-44cf85c32a41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="84c838da6aa04a0f137f8b0aba02cfe1" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B8F814574E960A4499025803604D4DF4" ma:contentTypeVersion="9" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="613b0908c48a25395136f5b5d1e9264a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b2ff61d-e0c4-454b-ba72-44cf85c32a41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5652efc65d8021725ff526b59607fd6" ns2:_="">
     <xsd:import namespace="4b2ff61d-e0c4-454b-ba72-44cf85c32a41"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -6378,8 +6385,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6487,7 +6494,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FF1424A-F6F1-4CD1-BE68-2CB4EF7D0F52}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0820833D-1D6B-4638-A6EE-FFF8DB82E1E1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
